--- a/02_DIA_inicio_2026_analisis_assets/rbd_9410_escuela-consolidada-davila_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9410_escuela-consolidada-davila_nt2_rubricas.xlsx
@@ -1788,13 +1788,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05894156-9311-4DEB-A9CE-146736C7F22C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDC9B131-92B2-4D03-91E7-EA4BA9EC088F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{682E79CD-C57E-437D-B28A-77921101E1A1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0816FB4C-633B-4321-8A0E-81B111FECF43}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA697B2E-56BC-42A5-AF6E-37433E65014F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F34C523-E85B-4812-9698-B0F2987EEABF}"/>
 </file>